--- a/SpringBoot前沿技术栈/14_SpringBoot-Excel/工作簿ReadDemo2.xlsx
+++ b/SpringBoot前沿技术栈/14_SpringBoot-Excel/工作簿ReadDemo2.xlsx
@@ -1,16 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14040"/>
+    <workbookView windowWidth="29400" windowHeight="14120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -49,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -108,7 +121,7 @@
     </r>
   </si>
   <si>
-    <t>游诗成</t>
+    <t>游家纨绔</t>
   </si>
   <si>
     <r>
@@ -126,7 +139,7 @@
     <t>Sheet1!B3</t>
   </si>
   <si>
-    <t>曹玉敏</t>
+    <t>小曹姐姐</t>
   </si>
   <si>
     <r>
@@ -204,31 +217,7 @@
     <t>百分比</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>游诗成</t>
-    </r>
-  </si>
-  <si>
     <t>ysc</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>曹玉敏</t>
-    </r>
   </si>
   <si>
     <t>cym</t>
@@ -243,7 +232,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -865,7 +854,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -879,9 +868,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -1434,19 +1420,19 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2" ht="17" spans="1:8">
       <c r="A2" s="4">
@@ -1458,19 +1444,19 @@
       <c r="C2" s="4">
         <v>1</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="1">
         <v>1.23</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>45153.9444444444</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>0.755</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1484,19 +1470,19 @@
       <c r="C3" s="4">
         <v>2.1</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="1">
         <v>2.34</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>45154.9444444444</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>0.856</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" ht="17" spans="1:8">
       <c r="A4" s="4">
@@ -1508,19 +1494,19 @@
       <c r="C4" s="4">
         <v>5.3</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="1">
         <v>3.45</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>45155.9444444444</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>0.954</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1568,12 +1554,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" ht="17" spans="1:7">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -1582,7 +1568,7 @@
         <v>1.23</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2">
         <v>45153.9444444444</v>
@@ -1591,12 +1577,12 @@
         <v>0.755</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:7">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>2.1</v>
@@ -1605,7 +1591,7 @@
         <v>2.34</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="2">
         <v>45154.9444444444</v>
@@ -1619,7 +1605,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1">
         <v>5.3</v>
@@ -1628,7 +1614,7 @@
         <v>3.45</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F4" s="2">
         <v>45155.9444444444</v>
